--- a/artfynd/A 18577-2024 artfynd.xlsx
+++ b/artfynd/A 18577-2024 artfynd.xlsx
@@ -1002,7 +1002,7 @@
         <v>117521407</v>
       </c>
       <c r="B5" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 18577-2024 artfynd.xlsx
+++ b/artfynd/A 18577-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>115504332</v>
       </c>
       <c r="B2" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,54 +776,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115504341</v>
+        <v>116668456</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4660</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Notsjön, Vb</t>
+          <t>notsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>767422</v>
+        <v>767358</v>
       </c>
       <c r="R3" t="n">
-        <v>7157778</v>
+        <v>7157798</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -855,12 +844,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2024-05-02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>stor aspklon</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -876,49 +870,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sven Bengtsson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116668456</v>
+        <v>117521407</v>
       </c>
       <c r="B4" t="n">
-        <v>90432</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4660</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,14 +916,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>notsjöbäcken, Vb</t>
+          <t>Notsjöbäcken, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>767358</v>
+        <v>767331</v>
       </c>
       <c r="R4" t="n">
-        <v>7157798</v>
+        <v>7157839</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,17 +950,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-02</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>stor aspklon</t>
+          <t>2024-05-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,65 +971,61 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Sven Bengtsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Sven Bengtsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117521407</v>
+        <v>115504341</v>
       </c>
       <c r="B5" t="n">
-        <v>78482</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Notsjöbäcken, Vb</t>
+          <t>Notsjön, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>767331</v>
+        <v>767422</v>
       </c>
       <c r="R5" t="n">
-        <v>7157839</v>
+        <v>7157778</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,12 +1052,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2023-10-08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-05-13</t>
+          <t>2023-10-08</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 18577-2024 artfynd.xlsx
+++ b/artfynd/A 18577-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115504332</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116668456</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117521407</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,8 +1102,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115504341</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>